--- a/Mosacvevebi.xlsx
+++ b/Mosacvevebi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Masho&amp;Gio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{544DB241-51B1-49D0-9C5A-F9FCB9455F93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F897C96-AC36-41DD-A1BC-0C2CA9F7B128}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -259,9 +259,6 @@
     <t>Keti Jangveladze &amp; Anzor Gogiberidze</t>
   </si>
   <si>
-    <t>ქეტი ჯანგველაძე &amp; ანზორ გოგიბერიძე</t>
-  </si>
-  <si>
     <t>https://augustwedding.github.io/mg/?guest=27</t>
   </si>
   <si>
@@ -547,9 +544,6 @@
     <t>Tornike Chikvaidze &amp; Keti Chikvaidze</t>
   </si>
   <si>
-    <t>თორნიკე ჩიკვაიძე &amp; ქეტი ჩიკვაიძე</t>
-  </si>
-  <si>
     <t>https://augustwedding.github.io/mg/?guest=59</t>
   </si>
   <si>
@@ -875,6 +869,12 @@
   </si>
   <si>
     <t>https://augustwedding.github.io/mg/?guest=95</t>
+  </si>
+  <si>
+    <t>ქეთი ჯანგველაძე &amp; ანზორ გოგიბერიძე</t>
+  </si>
+  <si>
+    <t>თორნიკე ჩიკვაიძე &amp; ქეთი ჩიკვაიძე</t>
   </si>
 </sst>
 </file>
@@ -1553,758 +1553,758 @@
         <v>78</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="C27" t="s">
         <v>79</v>
-      </c>
-      <c r="C27" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A28" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="C28" t="s">
         <v>82</v>
-      </c>
-      <c r="C28" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A29" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="C29" t="s">
         <v>85</v>
-      </c>
-      <c r="C29" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A30" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="C30" t="s">
         <v>88</v>
-      </c>
-      <c r="C30" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A31" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="C31" t="s">
         <v>91</v>
-      </c>
-      <c r="C31" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A32" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="C32" t="s">
         <v>94</v>
-      </c>
-      <c r="C32" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A33" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="C33" t="s">
         <v>97</v>
-      </c>
-      <c r="C33" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A34" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="C34" t="s">
         <v>100</v>
-      </c>
-      <c r="C34" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A35" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="C35" t="s">
         <v>103</v>
-      </c>
-      <c r="C35" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A36" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="C36" t="s">
         <v>106</v>
-      </c>
-      <c r="C36" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A37" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="C37" t="s">
         <v>109</v>
-      </c>
-      <c r="C37" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A38" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="C38" t="s">
         <v>112</v>
-      </c>
-      <c r="C38" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A39" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="C39" t="s">
         <v>115</v>
-      </c>
-      <c r="C39" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A40" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="C40" t="s">
         <v>118</v>
-      </c>
-      <c r="C40" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A41" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="C41" t="s">
         <v>121</v>
-      </c>
-      <c r="C41" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A42" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="C42" t="s">
         <v>124</v>
-      </c>
-      <c r="C42" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A43" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="C43" t="s">
         <v>127</v>
-      </c>
-      <c r="C43" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A44" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="C44" t="s">
         <v>130</v>
-      </c>
-      <c r="C44" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A45" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="C45" t="s">
         <v>133</v>
-      </c>
-      <c r="C45" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A46" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="C46" t="s">
         <v>136</v>
-      </c>
-      <c r="C46" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A47" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="C47" t="s">
         <v>139</v>
-      </c>
-      <c r="C47" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A48" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="C48" t="s">
         <v>142</v>
-      </c>
-      <c r="C48" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A49" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="C49" t="s">
         <v>145</v>
-      </c>
-      <c r="C49" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A50" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="C50" t="s">
         <v>148</v>
-      </c>
-      <c r="C50" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A51" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="C51" t="s">
         <v>151</v>
-      </c>
-      <c r="C51" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A52" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="C52" t="s">
         <v>154</v>
-      </c>
-      <c r="C52" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A53" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="C53" t="s">
         <v>157</v>
-      </c>
-      <c r="C53" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A54" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="C54" t="s">
         <v>160</v>
-      </c>
-      <c r="C54" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A55" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="C55" t="s">
         <v>163</v>
-      </c>
-      <c r="C55" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A56" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="C56" t="s">
         <v>166</v>
-      </c>
-      <c r="C56" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A57" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="C57" t="s">
         <v>169</v>
-      </c>
-      <c r="C57" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A58" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="C58" t="s">
         <v>172</v>
-      </c>
-      <c r="C58" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A59" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="C59" t="s">
         <v>174</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="C59" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A60" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C60" t="s">
         <v>177</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="C60" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A61" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C61" t="s">
         <v>180</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="C61" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A62" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C62" t="s">
         <v>183</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="C62" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A63" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C63" t="s">
         <v>186</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="C63" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A64" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C64" t="s">
         <v>189</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="C64" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A65" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C65" t="s">
         <v>192</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="C65" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A66" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C66" t="s">
         <v>195</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="C66" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A67" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C67" t="s">
         <v>198</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="C67" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A68" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C68" t="s">
         <v>201</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="C68" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="69" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A69" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C69" t="s">
         <v>204</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="C69" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A70" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C70" t="s">
         <v>207</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="C70" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="71" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A71" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C71" t="s">
         <v>210</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="C71" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A72" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C72" t="s">
         <v>213</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="C72" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="73" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A73" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C73" t="s">
         <v>216</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="C73" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A74" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C74" t="s">
         <v>219</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="C74" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="75" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A75" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C75" t="s">
         <v>222</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="C75" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A76" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C76" t="s">
         <v>225</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="C76" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="77" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A77" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C77" t="s">
         <v>228</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="C77" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="78" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A78" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C78" t="s">
         <v>231</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="C78" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="79" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A79" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C79" t="s">
         <v>234</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="C79" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="80" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A80" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C80" t="s">
         <v>237</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="C80" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A81" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C81" t="s">
         <v>240</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="C81" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A82" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C82" t="s">
         <v>243</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="C82" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A83" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C83" t="s">
         <v>246</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="C83" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="84" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A84" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C84" t="s">
         <v>249</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="C84" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A85" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C85" t="s">
         <v>252</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="C85" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="86" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A86" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C86" t="s">
         <v>255</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="C86" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="87" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A87" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C87" t="s">
         <v>258</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="C87" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="88" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A88" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C88" t="s">
         <v>261</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="C88" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="89" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A89" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C89" t="s">
         <v>264</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="C89" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="90" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A90" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="C90" t="s">
         <v>267</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="C90" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="91" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A91" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C91" t="s">
         <v>270</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="C91" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="92" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A92" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C92" t="s">
         <v>273</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="C92" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="93" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A93" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="C93" t="s">
         <v>276</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="C93" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="94" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A94" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C94" t="s">
         <v>279</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="C94" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="95" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A95" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="C95" t="s">
         <v>282</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="C95" t="s">
-        <v>284</v>
       </c>
     </row>
   </sheetData>

--- a/Mosacvevebi.xlsx
+++ b/Mosacvevebi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Masho&amp;Gio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F897C96-AC36-41DD-A1BC-0C2CA9F7B128}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2F6093F-B52A-4EFC-8911-F3EB6DF80CE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="288">
   <si>
     <t>En</t>
   </si>
@@ -875,13 +875,22 @@
   </si>
   <si>
     <t>თორნიკე ჩიკვაიძე &amp; ქეთი ჩიკვაიძე</t>
+  </si>
+  <si>
+    <t>Giga Pirskhalava</t>
+  </si>
+  <si>
+    <t>გიგა ფირცხალავა</t>
+  </si>
+  <si>
+    <t>https://augustwedding.github.io/mg/?guest=96</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -892,6 +901,14 @@
     <font>
       <sz val="16"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -914,14 +931,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1254,7 +1274,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C95"/>
+  <dimension ref="A1:C96"/>
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="51.5" bestFit="1" customWidth="1"/>
@@ -2307,7 +2327,21 @@
         <v>282</v>
       </c>
     </row>
+    <row r="96" spans="1:3" ht="21" x14ac:dyDescent="0.5">
+      <c r="A96" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C96" r:id="rId1" xr:uid="{EF465E93-8F15-4C70-AB39-DBE41FB7D097}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
